--- a/forms/trg/Formulir_TRG_coastaldw.xlsx
+++ b/forms/trg/Formulir_TRG_coastaldw.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B31)</f>
+        <f>COUNTA(Anggota!B5:B32)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F31)</f>
+        <f>COUNTA(Anggota!F5:F32)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Anwar Daud, S.KM., M.Kes.</t>
+          <t>Dr. Agus Bintara Birawida, S.Kel., M.Kes</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Focused on environmental quality assessment, clean water supply, Environmental Health Risk Assessment (EHRA), and AMDAL</t>
+          <t>Expert in coastal environmental health, drinking water quality, Environmental Health Risk Assessment (EHRA).</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,13 +937,13 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-6236-6097</t>
+          <t>0000-0002-8223-2387</t>
         </is>
       </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57218129458</t>
+          <t>57193116626</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,22 +958,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Ir. Nur An-Nisa Putry Mangarengi, S.T., M.Sc</t>
+          <t>Prof. Dr. Anwar Daud, S.KM., M.Kes.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Department of Environmental Engineering, Faculty of Engineering, Hasanuddin University</t>
+          <t>Department of Environmental Health, Public Health Faculty, Hasanuddin University</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Focused on water quality.</t>
+          <t>Focused on environmental quality assessment, clean water supply, Environmental Health Risk Assessment (EHRA), and AMDAL</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,13 +982,13 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-9308-4658</t>
+          <t>0000-0002-6236-6097</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57214988483</t>
+          <t>57218129458</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Muh Fajaruddin Natsir, S.KM.M.,Kes</t>
+          <t>Ir. Nur An-Nisa Putry Mangarengi, S.T., M.Sc</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Department of Environmental Health, Public Health Faculty, Hasanuddin University</t>
+          <t>Department of Environmental Engineering, Faculty of Engineering, Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Focused on water quality, water and wastewater treatment technologies, and community-based solid waste management.</t>
+          <t>Focused on water quality.</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1027,13 +1027,13 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1585-1169</t>
+          <t>0000-0002-9308-4658</t>
         </is>
       </c>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57208302128</t>
+          <t>57214988483</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Owildan Wisudawan B, S.KM., M.Kes</t>
+          <t>Muh Fajaruddin Natsir, S.KM.M.,Kes</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Expert in Environmental Health Microbiology</t>
+          <t>Focused on water quality, water and wastewater treatment technologies, and community-based solid waste management.</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1072,13 +1072,13 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2300-0049</t>
+          <t>0000-0003-1585-1169</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>59419526900</t>
+          <t>57208302128</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1093,22 +1093,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Shaharuddin Mohd. Sham</t>
+          <t>Dr. Owildan Wisudawan B, S.KM., M.Kes</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Faculty Of Medicine and Health Sciences, University Putra Malaysia</t>
+          <t>Department of Environmental Health, Public Health Faculty, Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Focused on water quality, groundwater quality, and environmental health risk assessment (EHRA)</t>
+          <t>Expert in Environmental Health Microbiology</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1117,11 +1117,15 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-3603-0821</t>
+          <t>0000-0003-2300-0049</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>59419526900</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1134,29 +1138,33 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Umar Aminu Mohammed</t>
+          <t>Dr. Shaharuddin Mohd. Sham</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>SA'ADU ZUNGUR UNIVERSITY, Bauchi, Nigeria</t>
+          <t>Faculty Of Medicine and Health Sciences, University Putra Malaysia</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Applied Environmental Biology and Ecology</t>
+          <t>Focused on water quality, groundwater quality, and environmental health risk assessment (EHRA)</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-3603-0821</t>
+        </is>
+      </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
@@ -1171,12 +1179,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Shehu Abubakar Kafi</t>
+          <t>Dr. Umar Aminu Mohammed</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1186,7 +1194,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Hydrobiology, Fisheries, Aquatic Toxicology</t>
+          <t>Applied Environmental Biology and Ecology</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1208,22 +1216,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Fahmi Aziz, S.KM., M.Sc</t>
+          <t>Shehu Abubakar Kafi</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Department of Human Ecology, School of International Health, University of Tokyo</t>
+          <t>SA'ADU ZUNGUR UNIVERSITY, Bauchi, Nigeria</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Human Ecology, Environment</t>
+          <t>Hydrobiology, Fisheries, Aquatic Toxicology</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1245,33 +1253,29 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Nurlia Sila, SKM.M.KL</t>
+          <t>Muhammad Fahmi Aziz, S.KM., M.Sc</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Department of Environmental Health, Public Health Faculty, Hasanuddin University</t>
+          <t>Department of Human Ecology, School of International Health, University of Tokyo</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Focused on environmental remediation and Environmental Health Risk Assessment (EHRA).</t>
+          <t>Human Ecology, Environment</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-9612-159X</t>
-        </is>
-      </c>
+      <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="inlineStr">
@@ -1286,29 +1290,33 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Ain Khaer, S.ST., M.Kes</t>
+          <t>Nurlia Sila, SKM.M.KL</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Environmental Science Study Program, Postgraduate School, Hasanuddin University</t>
+          <t>Department of Environmental Health, Public Health Faculty, Hasanuddin University</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Focused on environmental health, water quality, and environmental sanitation</t>
+          <t>Focused on environmental remediation and Environmental Health Risk Assessment (EHRA).</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-9612-159X</t>
+        </is>
+      </c>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="11" t="inlineStr">
@@ -1323,22 +1331,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Musfira Ramadhani Syamsir, S.KM., M.KL</t>
+          <t>Ain Khaer, S.ST., M.Kes</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Department of Environmental Health, Public Health Faculty, Hasanuddin University</t>
+          <t>Environmental Science Study Program, Postgraduate School, Hasanuddin University</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Envoromental Health</t>
+          <t>Focused on environmental health, water quality, and environmental sanitation</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1360,22 +1368,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Sukmawati</t>
+          <t>Musfira Ramadhani Syamsir, S.KM., M.KL</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Department of Environmental Health, Public Health Faculty, Hasanuddin University</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Doctoral Postgraduate Student</t>
+          <t>Envoromental Health</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1397,12 +1405,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>La Ode Tasrun</t>
+          <t>Sukmawati</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1434,12 +1442,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Pitriani</t>
+          <t>La Ode Tasrun</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1471,22 +1479,22 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Marwah Nur Fajrin</t>
+          <t>Pitriani</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Magister students</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>CDW Team</t>
+          <t>Doctoral Postgraduate Student</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -1506,10 +1514,26 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="11" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Marwah Nur Fajrin</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Magister students</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>CDW Team</t>
+        </is>
+      </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
@@ -1517,7 +1541,11 @@
       <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1706,15 +1734,32 @@
       <c r="L31" s="12" t="n"/>
       <c r="M31" s="12" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
